--- a/channels.xlsx
+++ b/channels.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
   <si>
     <r>
       <rPr>
@@ -24,34 +24,21 @@
     </r>
   </si>
   <si>
+    <t/>
+  </si>
+  <si>
     <r>
-      <rPr>
-        <b/>
-        <color rgb="FFBBBEBF"/>
-      </rPr>
-      <t>@ankhahy</t>
+      <t>UCWeBdGB3GyRRJfoGPJ46-_Q</t>
     </r>
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <color rgb="FFBBBEBF"/>
-      </rPr>
-      <t>ankhahy</t>
+      <t>@XuanLin</t>
     </r>
   </si>
   <si>
     <r>
-      <t>UCp8cPvx_Od76EL66vvCnhRA</t>
-    </r>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <r>
-      <t>浙江卫视音乐频道 ZJSTV Music Channel</t>
+      <t>林宣 Xuan Lin</t>
     </r>
   </si>
 </sst>
@@ -423,34 +410,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/channels.xlsx
+++ b/channels.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
   <si>
     <r>
       <rPr>
@@ -24,7 +24,12 @@
     </r>
   </si>
   <si>
-    <t/>
+    <r>
+      <rPr>
+        <b/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <r>
@@ -39,6 +44,136 @@
   <si>
     <r>
       <t>林宣 Xuan Lin</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCF3XD6Aabi62TAT9lVBHDQA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@millyyang101</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>楊楊Milly Yang</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCfq75-6J5seC82CmtLSFxXw</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@TheDoDoMen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>The DoDo Men 嘟嘟人</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCbIJeyl_va8MG2xx0q4Uobg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@helloiamhook</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Hook</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UC0YAgB-kCdyxBX1lB-oS7cg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@LenaPatrickTaiwan</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>旅遊真台灣 Lena &amp; Patrick</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCa7c1phjUa5UMWS68Ybgrdg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@elephantgogo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>小象愛出門</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCFycVZXj9fRWB_OZfFKe2PA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@happyariel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>欸你這週要幹嘛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@Traveggo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>找蔬食Traveggo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCghPiQIi_uyjF1YHKj-FhGw</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@TKstorytw</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>台客劇場</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCtDL1RpW8r_Fg7D0aoFAqQw</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>@celineswaytravel</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Celine's Way 不只是旅行</t>
     </r>
   </si>
 </sst>
@@ -394,7 +529,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -426,18 +561,98 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>1</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/channels.xlsx
+++ b/channels.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="32">
   <si>
     <r>
       <rPr>
@@ -134,6 +134,11 @@
   <si>
     <r>
       <t>欸你這週要幹嘛</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>UCUJdsQghaciVvOmwz7kxqzA</t>
     </r>
   </si>
   <si>
@@ -625,34 +630,37 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
